--- a/results_len4_comparison.xlsx
+++ b/results_len4_comparison.xlsx
@@ -38,7 +38,7 @@
       <color rgb="00666666"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -119,9 +114,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -493,8 +485,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -508,12 +500,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Cases Done</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Cases in Common</t>
+          <t>Total Cases</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -539,19 +531,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>10.2</v>
+        <v>15.3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0075</v>
+        <v>0.0081</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>48.5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
@@ -561,19 +553,19 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>27.1</v>
+        <v>34.1</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0167</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>104.7</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4">
@@ -583,19 +575,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.0834</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>223</v>
+        <v>233.3</v>
       </c>
     </row>
     <row r="5">
@@ -605,25 +597,25 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>20.3</v>
+        <v>22.4</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.0186</v>
+        <v>0.0178</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>134.9</v>
+        <v>306.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Accuracy / Cost / Latency computed over 59 cases done in all 4 methods.</t>
+          <t>Accuracy over all 85 cases (missing cases counted as failed). Avg Cost and Latency computed only over cases with logged data.</t>
         </is>
       </c>
     </row>
@@ -1266,9 +1258,9 @@
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
         </is>
       </c>
     </row>
@@ -1288,14 +1280,14 @@
           <t>Correct</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
         </is>
       </c>
     </row>
@@ -1315,14 +1307,14 @@
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -1342,14 +1334,14 @@
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -1369,14 +1361,14 @@
           <t>Correct</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
         </is>
       </c>
     </row>
@@ -1396,14 +1388,14 @@
           <t>Correct</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
         </is>
       </c>
     </row>
@@ -1423,14 +1415,14 @@
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -1450,14 +1442,14 @@
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -1467,24 +1459,24 @@
           <t>4_44</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
         </is>
       </c>
     </row>
@@ -1494,24 +1486,24 @@
           <t>4_45</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -1521,24 +1513,24 @@
           <t>4_46</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -1548,24 +1540,24 @@
           <t>4_47</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -1953,14 +1945,14 @@
           <t>4_62</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -1980,14 +1972,14 @@
           <t>4_63</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2007,14 +1999,14 @@
           <t>4_64</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2211,9 +2203,9 @@
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -2238,9 +2230,9 @@
           <t>Correct</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -2265,9 +2257,9 @@
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -2292,9 +2284,9 @@
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -2319,9 +2311,9 @@
           <t>Correct</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -2346,9 +2338,9 @@
           <t>Correct</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
         </is>
       </c>
     </row>
@@ -2373,9 +2365,9 @@
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -2400,9 +2392,9 @@
           <t>Incorrect</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Correct</t>
         </is>
       </c>
     </row>
@@ -2427,9 +2419,9 @@
           <t>Correct</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -2449,14 +2441,14 @@
           <t>Correct</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -2628,14 +2620,14 @@
           <t>4_87</t>
         </is>
       </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>Remaining</t>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
